--- a/final_data_pipeline/output/311513longform_elec_options_nowhp.xlsx
+++ b/final_data_pipeline/output/311513longform_elec_options_nowhp.xlsx
@@ -691,7 +691,7 @@
         <v>44</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="J4">
         <v>8000</v>
@@ -706,10 +706,10 @@
         <v>919063.5325570232</v>
       </c>
       <c r="N4">
-        <v>1.741590909090909</v>
+        <v>1.782371783972741</v>
       </c>
       <c r="O4">
-        <v>1.89075</v>
+        <v>1.939565227172176</v>
       </c>
       <c r="P4">
         <v>114.8829415696279</v>
@@ -744,7 +744,7 @@
         <v>44</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="J5">
         <v>8000</v>
@@ -759,10 +759,10 @@
         <v>402269.0602377881</v>
       </c>
       <c r="N5">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="O5">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="P5">
         <v>50.28363252972352</v>
@@ -797,7 +797,7 @@
         <v>44</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="J6">
         <v>8000</v>
@@ -812,10 +812,10 @@
         <v>464597.8028598594</v>
       </c>
       <c r="N6">
-        <v>1.741590909090909</v>
+        <v>1.62249843161857</v>
       </c>
       <c r="O6">
-        <v>1.89075</v>
+        <v>1.749494516792324</v>
       </c>
       <c r="P6">
         <v>58.07472535748242</v>
@@ -850,7 +850,7 @@
         <v>45</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="J7">
         <v>8000</v>
@@ -897,7 +897,7 @@
         <v>44</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="J8">
         <v>8000</v>
@@ -912,10 +912,10 @@
         <v>1513735.044102835</v>
       </c>
       <c r="N8">
-        <v>1.741590909090909</v>
+        <v>1.784885911058073</v>
       </c>
       <c r="O8">
-        <v>1.89075</v>
+        <v>1.942582169301264</v>
       </c>
       <c r="P8">
         <v>189.2168805128543</v>
@@ -950,7 +950,7 @@
         <v>45</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="J9">
         <v>8000</v>
@@ -1050,7 +1050,7 @@
         <v>44</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="J11">
         <v>8000</v>
@@ -1065,10 +1065,10 @@
         <v>633640.9078500222</v>
       </c>
       <c r="N11">
-        <v>1.741590909090909</v>
+        <v>1.554711451758341</v>
       </c>
       <c r="O11">
-        <v>1.89075</v>
+        <v>1.669946025515211</v>
       </c>
       <c r="P11">
         <v>79.20511348125278</v>
@@ -1256,7 +1256,7 @@
         <v>44</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="J15">
         <v>8000</v>
@@ -1271,10 +1271,10 @@
         <v>637800.9771343042</v>
       </c>
       <c r="N15">
-        <v>1.741590909090909</v>
+        <v>1.62249843161857</v>
       </c>
       <c r="O15">
-        <v>1.89075</v>
+        <v>1.749494516792324</v>
       </c>
       <c r="P15">
         <v>79.72512214178803</v>
@@ -1309,7 +1309,7 @@
         <v>44</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J16">
         <v>8000</v>
@@ -1324,10 +1324,10 @@
         <v>611453.3696071696</v>
       </c>
       <c r="N16">
-        <v>1.741590909090909</v>
+        <v>1.929056920423291</v>
       </c>
       <c r="O16">
-        <v>1.89075</v>
+        <v>2.117059768804106</v>
       </c>
       <c r="P16">
         <v>76.4316712008962</v>
@@ -1362,7 +1362,7 @@
         <v>45</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J17">
         <v>8000</v>
@@ -1409,7 +1409,7 @@
         <v>44</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="J18">
         <v>8000</v>
@@ -1424,10 +1424,10 @@
         <v>337331.1063640936</v>
       </c>
       <c r="N18">
-        <v>1.741590909090909</v>
+        <v>1.8239809580482</v>
       </c>
       <c r="O18">
-        <v>1.89075</v>
+        <v>1.989608681354817</v>
       </c>
       <c r="P18">
         <v>42.16638829551169</v>
@@ -1462,7 +1462,7 @@
         <v>44</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="J19">
         <v>8000</v>
@@ -1477,10 +1477,10 @@
         <v>459005.3563527851</v>
       </c>
       <c r="N19">
-        <v>1.741590909090909</v>
+        <v>1.62249843161857</v>
       </c>
       <c r="O19">
-        <v>1.89075</v>
+        <v>1.749494516792324</v>
       </c>
       <c r="P19">
         <v>57.37566954409814</v>
@@ -1515,7 +1515,7 @@
         <v>44</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="J20">
         <v>8000</v>
@@ -1530,10 +1530,10 @@
         <v>564064.4268514247</v>
       </c>
       <c r="N20">
-        <v>1.741590909090909</v>
+        <v>1.554711451758341</v>
       </c>
       <c r="O20">
-        <v>1.89075</v>
+        <v>1.669946025515211</v>
       </c>
       <c r="P20">
         <v>70.50805335642809</v>
@@ -1568,7 +1568,7 @@
         <v>45</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="J21">
         <v>8000</v>
